--- a/Transmitter/Probe_Model/Probe_Model_Results.xlsx
+++ b/Transmitter/Probe_Model/Probe_Model_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoa-my.sharepoint.com/personal/jstr633_uoa_auckland_ac_nz/Documents/Documents/Engineering/Part 3/ELECTENG 310/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kburd\Projects\310_Projects\310-water-sensing\Transmitter\Probe_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="12" documentId="8_{470A86D2-07FA-42C3-A968-C3F1F66E2417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8427E4C8-FEA8-4672-8FCD-45230201A9DB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{F145DA7B-FC01-4C9B-B2EC-340B2B2846E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F145DA7B-FC01-4C9B-B2EC-340B2B2846E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Silicone Rubber" sheetId="4" r:id="rId1"/>
@@ -503,7 +503,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -521,7 +521,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1252,7 +1252,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2911,10 +2911,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3233,22 +3229,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9D220C9-0485-4A45-A12F-807F02B58A2A}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.73046875" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1328125" customWidth="1"/>
-    <col min="12" max="12" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -3268,7 +3264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -3294,7 +3290,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="37"/>
       <c r="D3" s="6" t="s">
         <v>10</v>
@@ -3319,7 +3315,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3344,7 +3340,7 @@
       <c r="J4" s="3"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
@@ -3372,7 +3368,7 @@
       </c>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="36" t="s">
         <v>24</v>
       </c>
@@ -3396,7 +3392,7 @@
       <c r="J6" s="3"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="37"/>
       <c r="D7" s="6" t="s">
         <v>9</v>
@@ -3420,7 +3416,7 @@
         <v>338.06339999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="8"/>
       <c r="D8" s="4" t="s">
         <v>0</v>
@@ -3441,7 +3437,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="9"/>
       <c r="D9" s="6" t="s">
         <v>17</v>
@@ -3465,7 +3461,7 @@
         <v>212.99699999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="8"/>
       <c r="D10" s="4" t="s">
         <v>8</v>
@@ -3486,7 +3482,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="9"/>
       <c r="D11" s="6" t="s">
         <v>7</v>
@@ -3510,7 +3506,7 @@
         <v>187.98360000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="36" t="s">
         <v>23</v>
       </c>
@@ -3533,7 +3529,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="37"/>
       <c r="D13" s="6" t="s">
         <v>5</v>
@@ -3571,22 +3567,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE338397-36C7-458A-BCE9-0F63808AB4B3}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.265625" customWidth="1"/>
-    <col min="3" max="3" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1328125" customWidth="1"/>
-    <col min="12" max="12" width="17.59765625" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.21875" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -3606,7 +3602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -3632,7 +3628,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="37"/>
       <c r="D3" s="6" t="s">
         <v>10</v>
@@ -3657,7 +3653,7 @@
       </c>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3682,7 +3678,7 @@
       <c r="J4" s="3"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
@@ -3710,7 +3706,7 @@
       </c>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="36" t="s">
         <v>24</v>
       </c>
@@ -3734,7 +3730,7 @@
       <c r="J6" s="3"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="37"/>
       <c r="D7" s="6" t="s">
         <v>9</v>
@@ -3758,7 +3754,7 @@
         <v>745.10800000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="22"/>
       <c r="D8" s="4" t="s">
         <v>0</v>
@@ -3779,7 +3775,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="25"/>
       <c r="D9" s="6" t="s">
         <v>17</v>
@@ -3803,7 +3799,7 @@
         <v>444.15060000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="22"/>
       <c r="D10" s="4" t="s">
         <v>8</v>
@@ -3824,7 +3820,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="25"/>
       <c r="D11" s="6" t="s">
         <v>7</v>
@@ -3848,7 +3844,7 @@
         <v>383.6336</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="36" t="s">
         <v>23</v>
       </c>
@@ -3871,7 +3867,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="37"/>
       <c r="D13" s="6" t="s">
         <v>5</v>
@@ -3908,14 +3904,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EE75867-1AFD-4518-8061-84685FFA86D8}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -3926,7 +3922,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3937,7 +3933,7 @@
         <v>142.65219999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>625</v>
       </c>
@@ -3948,7 +3944,7 @@
         <v>444.15060000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1250</v>
       </c>
@@ -3959,7 +3955,7 @@
         <v>745.10800000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1875</v>
       </c>
@@ -3970,7 +3966,7 @@
         <v>1046.5708</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2500</v>
       </c>
@@ -3990,20 +3986,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5294AB7E-D769-47BB-9D65-6EE913DA0CE8}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.9296875" customWidth="1"/>
-    <col min="3" max="3" width="14.19921875" customWidth="1"/>
-    <col min="4" max="4" width="15.46484375" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="6" width="11" style="31" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.796875" style="30" customWidth="1"/>
-    <col min="9" max="9" width="14.796875" customWidth="1"/>
-    <col min="10" max="10" width="22.46484375" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" style="30" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="16.2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -4023,7 +4019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5.9880000000000003E-2</v>
       </c>
@@ -4046,7 +4042,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C3" s="32">
         <v>0.25</v>
       </c>
@@ -4066,7 +4062,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C4" s="32">
         <v>0.5</v>
       </c>
@@ -4086,7 +4082,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" s="32">
         <v>0.75</v>
       </c>
@@ -4106,7 +4102,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" s="32">
         <v>1</v>
       </c>
@@ -4126,19 +4122,19 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E7" s="29"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8" s="29"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E9" s="29"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E10" s="29"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E11" s="29"/>
       <c r="I11" s="3"/>
     </row>
